--- a/data/trending_integrated_20260918_10.xlsx
+++ b/data/trending_integrated_20260918_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8410</v>
+        <v>8330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.80%</t>
+          <t>'+18.66%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.59</v>
       </c>
       <c r="O2" t="n">
-        <v>112202078105</v>
+        <v>116611240340</v>
       </c>
       <c r="P2" t="n">
         <v>16200</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>우리로, 상한가 안착 시 10000원 돌파 및 텐베거 기대. 일부 투자자는 '사기주식' 언급.</t>
+          <t>일부 투자자 손절 및 매도 의견 존재. 8,000원 안착 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['상한가', '텐베거', '사기주식']</t>
+          <t>['매도 의견', '손절', '8000원 안착']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6850</v>
+        <v>24750</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.50%</t>
+          <t>'+14.58%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.02</v>
+        <v>-0.2</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="H3" t="n">
-        <v>2.85</v>
+        <v>2.41</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5880</v>
+        <v>21600</v>
       </c>
       <c r="K3" t="n">
-        <v>5950</v>
+        <v>22250</v>
       </c>
       <c r="L3" t="n">
-        <v>6920</v>
+        <v>25150</v>
       </c>
       <c r="M3" t="n">
-        <v>5840</v>
+        <v>21700</v>
       </c>
       <c r="N3" t="n">
-        <v>1.83</v>
+        <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>63626544885</v>
+        <v>160988971575</v>
       </c>
       <c r="P3" t="n">
-        <v>11760</v>
+        <v>59600</v>
       </c>
       <c r="Q3" t="n">
-        <v>1620</v>
+        <v>1030</v>
       </c>
       <c r="R3" t="n">
-        <v>900000</v>
+        <v>-241000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>KBI메탈, 변압기 관련 기대감 속 가온전선과 비교. 종가상 가능성 및 7000원 저항선 언급.</t>
+          <t>박스권 상단 돌파 후 5~6만원대 재진입 및 25,000원 돌파 기대감. 통신주 테마 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['변압기', '가온전선', '7000원']</t>
+          <t>['박스권 돌파', '통신주', '25000원 돌파']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13370</v>
+        <v>13080</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.46%</t>
+          <t>'+12.95%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H4" t="n">
         <v>8.029999999999999</v>
@@ -794,7 +794,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>91030464630</v>
+        <v>95306191175</v>
       </c>
       <c r="P4" t="n">
         <v>21150</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>파미셀, 모더나 관련 호재 기대감 속 프로그램 매수 증가. 2030년까지 운세 상승 전망.</t>
+          <t>셀그램 관련 뉴스 기대감 있으나, 주가 변동성과 개인 손실 우려 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['모더나', '프로그램 매수', '호재']</t>
+          <t>['셀그램', '뉴스 기대', '주가 변동성']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24500</v>
+        <v>6620</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.43%</t>
+          <t>'+12.59%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.2</v>
+        <v>1.02</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="H5" t="n">
-        <v>2.41</v>
+        <v>2.85</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>21600</v>
+        <v>5880</v>
       </c>
       <c r="K5" t="n">
-        <v>22250</v>
+        <v>5950</v>
       </c>
       <c r="L5" t="n">
-        <v>25150</v>
+        <v>6920</v>
       </c>
       <c r="M5" t="n">
-        <v>21700</v>
+        <v>5840</v>
       </c>
       <c r="N5" t="n">
-        <v>2.61</v>
+        <v>1.83</v>
       </c>
       <c r="O5" t="n">
-        <v>151834722575</v>
+        <v>69273495875</v>
       </c>
       <c r="P5" t="n">
-        <v>59600</v>
+        <v>11760</v>
       </c>
       <c r="Q5" t="n">
-        <v>1030</v>
+        <v>1620</v>
       </c>
       <c r="R5" t="n">
-        <v>-241000</v>
+        <v>900000</v>
       </c>
       <c r="S5" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>성호전자, 박스권 상단 돌파 및 2차 VI 기대감. 5~6만원대 재진입 및 25000원 목표 언급.</t>
+          <t>가온전선과 비교하며 변압기 관련주로서의 상승 기대감 표시. 종가상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['박스권 돌파', 'VI', '25000원']</t>
+          <t>['변압기', '가온전선', '종가상승']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31700</v>
+        <v>17820</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.01%</t>
+          <t>'+10.48%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>-0.27</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>152</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="G6" t="n">
-        <v>53</v>
+        <v>958</v>
       </c>
       <c r="H6" t="n">
-        <v>11.44</v>
+        <v>4.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>28300</v>
+        <v>16130</v>
       </c>
       <c r="K6" t="n">
-        <v>28850</v>
+        <v>16360</v>
       </c>
       <c r="L6" t="n">
-        <v>31700</v>
+        <v>18230</v>
       </c>
       <c r="M6" t="n">
-        <v>28550</v>
+        <v>16170</v>
       </c>
       <c r="N6" t="n">
-        <v>11.46</v>
+        <v>4.88</v>
       </c>
       <c r="O6" t="n">
-        <v>96567905850</v>
+        <v>398755282540</v>
       </c>
       <c r="P6" t="n">
-        <v>75900</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>15000</v>
+        <v>1272</v>
       </c>
       <c r="R6" t="n">
-        <v>228000</v>
+        <v>474000</v>
       </c>
       <c r="S6" t="n">
-        <v>5000</v>
+        <v>90000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대한전선, 가온전선과의 비교 언급 속 주가 상승 기대. 골든크로스 형성 가능성 및 수급 동향 주시.</t>
+          <t>18,000원 돌파에 대한 기대감 고조. 광통신 관련 기업 주가 상승 소식.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['가온전선', '골든크로스', '수급']</t>
+          <t>['18000원 돌파', '광통신', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17960</v>
+        <v>31250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+11.35%</t>
+          <t>'+10.42%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.27</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>872</v>
+        <v>78</v>
       </c>
       <c r="H7" t="n">
-        <v>4.61</v>
+        <v>11.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16130</v>
+        <v>28300</v>
       </c>
       <c r="K7" t="n">
-        <v>16360</v>
+        <v>28850</v>
       </c>
       <c r="L7" t="n">
-        <v>18230</v>
+        <v>32050</v>
       </c>
       <c r="M7" t="n">
-        <v>16170</v>
+        <v>28550</v>
       </c>
       <c r="N7" t="n">
-        <v>4.88</v>
+        <v>11.46</v>
       </c>
       <c r="O7" t="n">
-        <v>377155566375</v>
+        <v>116369328250</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>75900</v>
       </c>
       <c r="Q7" t="n">
-        <v>1272</v>
+        <v>15000</v>
       </c>
       <c r="R7" t="n">
-        <v>474000</v>
+        <v>228000</v>
       </c>
       <c r="S7" t="n">
-        <v>90000</v>
+        <v>5000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대한광통신, ETF 대란 및 공매도 관련 언급. 18000원 돌파 기대 및 25층 추석 목표.</t>
+          <t>가온전선과의 비교 언급되며 상승 기대감 존재. 구리 490억원 매수 소식.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['ETF', '공매도', '18000원']</t>
+          <t>['구리 매수', '전선주', '상승 기대']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14210</v>
+        <v>13960</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+10.50%</t>
+          <t>'+8.55%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="H8" t="n">
         <v>2.83</v>
@@ -1162,7 +1162,7 @@
         <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>89293056495</v>
+        <v>103359406970</v>
       </c>
       <c r="P8" t="n">
         <v>20300</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대원전선, 미국 LA전력청 계약 및 미주 매출 폭증 뉴스 기반 주가 상승 기대. 프로그램 매수 유입.</t>
+          <t>수조원 규모 미국 LA 전력청 투자 가능성 제기. 제품 테스트 완료 및 미주 매출 3.5배 폭증 소식.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LA전력청', '미주 매출', '프로그램 매수']</t>
+          <t>['LA 전력청', '매출 폭증', '제품 테스트']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54900</v>
+        <v>54400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.44%</t>
+          <t>'+6.46%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="H9" t="n">
         <v>38.54</v>
@@ -1254,7 +1254,7 @@
         <v>38.62</v>
       </c>
       <c r="O9" t="n">
-        <v>132104301450</v>
+        <v>139070240950</v>
       </c>
       <c r="P9" t="n">
         <v>67300</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 외인·기관 매수세 유입 및 우상향 추세 전망. 52000~58000원대 돌파 기대.</t>
+          <t>외인·기관 매수세 유입에 따른 우상향 추세 전망. 52,000~53,000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인기관 매수', '우상향', '58000원']</t>
+          <t>['외인 매수', '우상향', '추세 전망']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19130</v>
+        <v>19530</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+6.69%</t>
+          <t>'+5.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.38</v>
+        <v>-0.11</v>
       </c>
       <c r="E10" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>152</v>
+        <v>219</v>
       </c>
       <c r="H10" t="n">
-        <v>0.98</v>
+        <v>10.74</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17930</v>
+        <v>18490</v>
       </c>
       <c r="K10" t="n">
-        <v>18400</v>
+        <v>18900</v>
       </c>
       <c r="L10" t="n">
-        <v>20400</v>
+        <v>19700</v>
       </c>
       <c r="M10" t="n">
-        <v>17910</v>
+        <v>18770</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6</v>
+        <v>10.85</v>
       </c>
       <c r="O10" t="n">
-        <v>56404660930</v>
+        <v>71707022490</v>
       </c>
       <c r="P10" t="n">
-        <v>21100</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>9900</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>24000</v>
+        <v>213000</v>
       </c>
       <c r="S10" t="n">
-        <v>22000</v>
+        <v>66000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>보호예수 물량 해제에 따른 주가 변동성 우려 속, 기술이전 기대감 및 긍정적 수급 분석.</t>
+          <t>미국 원전주 상승세 및 중동 전쟁 종전 기대감 속 주가 상승 전망. 대차해지 운동 참여 독려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보호예수', '기술이전', '수급']</t>
+          <t>['원전주', '대차해지', '중동 전쟁']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19680</v>
+        <v>1823000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.44%</t>
+          <t>'+4.47%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
+        <v>736</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>451</v>
       </c>
       <c r="G11" t="n">
-        <v>196</v>
+        <v>3089</v>
       </c>
       <c r="H11" t="n">
-        <v>10.74</v>
+        <v>50.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18490</v>
+        <v>1745000</v>
       </c>
       <c r="K11" t="n">
-        <v>18900</v>
+        <v>1810000</v>
       </c>
       <c r="L11" t="n">
-        <v>19680</v>
+        <v>1828000</v>
       </c>
       <c r="M11" t="n">
-        <v>18770</v>
+        <v>1805000</v>
       </c>
       <c r="N11" t="n">
-        <v>10.85</v>
+        <v>50.2</v>
       </c>
       <c r="O11" t="n">
-        <v>63383320185</v>
+        <v>1416356941500</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>333000</v>
       </c>
       <c r="R11" t="n">
-        <v>213000</v>
+        <v>129000</v>
       </c>
       <c r="S11" t="n">
-        <v>66000</v>
+        <v>65000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대우건설, 중동 전쟁 종전 및 대미 투자 발표에 따른 하반기 주가 상승 전망. 대차해지 운동 언급.</t>
+          <t>미국 증시 및 반도체주 급등에 따른 200만 돌파 기대. 공급 부족 장기화 전망 및 AI 두뇌 역할 강조.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['중동 전쟁', '대미 투자', '대차해지']</t>
+          <t>['반도체', 'AI', '공급 부족']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1824000</v>
+        <v>18730</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.53%</t>
+          <t>'+4.46%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1</v>
+        <v>0.38</v>
       </c>
       <c r="E12" t="n">
-        <v>707</v>
+        <v>83</v>
       </c>
       <c r="F12" t="n">
-        <v>437</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>3026</v>
+        <v>155</v>
       </c>
       <c r="H12" t="n">
-        <v>50.1</v>
+        <v>0.98</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1745000</v>
+        <v>17930</v>
       </c>
       <c r="K12" t="n">
-        <v>1810000</v>
+        <v>18400</v>
       </c>
       <c r="L12" t="n">
-        <v>1828000</v>
+        <v>20400</v>
       </c>
       <c r="M12" t="n">
-        <v>1805000</v>
+        <v>17910</v>
       </c>
       <c r="N12" t="n">
-        <v>50.2</v>
+        <v>0.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1288419539500</v>
+        <v>58712111425</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>21100</v>
       </c>
       <c r="Q12" t="n">
-        <v>333000</v>
+        <v>9900</v>
       </c>
       <c r="R12" t="n">
-        <v>129000</v>
+        <v>24000</v>
       </c>
       <c r="S12" t="n">
-        <v>65000</v>
+        <v>22000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 증시 및 반도체주 급등에 따른 200만 돌파 기대. 공급 부족 장기화 전망 및 AI 두뇌 역할 강조.</t>
+          <t>보호예수 물량 해제에 따른 주가 변동성 우려 속, 기술이전 기대감 및 긍정적 수급 분석.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '공급 부족']</t>
+          <t>['보호예수', '기술이전', '수급']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>259500</v>
+        <v>259000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.77%</t>
+          <t>'+2.57%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="G13" t="n">
-        <v>2921</v>
+        <v>2562</v>
       </c>
       <c r="H13" t="n">
         <v>46.48</v>
@@ -1622,7 +1622,7 @@
         <v>46.52</v>
       </c>
       <c r="O13" t="n">
-        <v>746435389750</v>
+        <v>812784412000</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>삼성전자, 정치적 이슈와 관련된 언급 다수. 30만 전자 재탈환 및 배당금 기대.</t>
+          <t>정치적 이슈 언급되며 주가 하락 우려 제기. 미국 국채 금리 하락 소식.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '배당금', '30만 전자']</t>
+          <t>['정치적 이슈', '국채 금리', '주가 조작']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17550</v>
+        <v>17540</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+1.68%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.27</v>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="H14" t="n">
         <v>0.97</v>
@@ -1714,7 +1714,7 @@
         <v>0.7</v>
       </c>
       <c r="O14" t="n">
-        <v>61030669285</v>
+        <v>62712651335</v>
       </c>
       <c r="P14" t="n">
         <v>30550</v>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터 주식 급등에 따른 관련주 동반 상승 기대. AI, 양자컴퓨터, 보안 테마 수혜 전망.</t>
+          <t>미국 증시 양자컴퓨터 및 보안 관련주 급등에 따른 엑스게이트의 상승 기대. AI, 반도체, 양자컴퓨터 테마 언급. 객관적 근거보다는 시장 분위기에 편승.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>85800</v>
+        <v>85500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G15" t="n">
-        <v>738</v>
+        <v>771</v>
       </c>
       <c r="H15" t="n">
         <v>23.23</v>
@@ -1806,7 +1806,7 @@
         <v>23.27</v>
       </c>
       <c r="O15" t="n">
-        <v>55672095400</v>
+        <v>59504065750</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 원전주 급등과 대미 투자 관련 발표 가능성 뉴스를 기반으로 주가 상승 기대감이 형성됨. 120일선 돌파 및 장기적 50만원 목표 제시.</t>
+          <t>미국 증시 원전주 급등 및 한미 외교장관 회담 계기 대미 투자 관련 발표 가능성 언급. 에너지 관리, GPU 전력 부족 뉴스와 연계. 일부 뉴스 기반.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전주', '대미 투자', '120일선']</t>
+          <t>['원자력', '대미투자', '에너지']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4190</v>
+        <v>4185</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-9.60%</t>
+          <t>'-9.71%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.4</v>
       </c>
       <c r="E16" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F16" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G16" t="n">
-        <v>530</v>
+        <v>559</v>
       </c>
       <c r="H16" t="n">
         <v>0.55</v>
@@ -1892,13 +1892,13 @@
         <v>4535</v>
       </c>
       <c r="M16" t="n">
-        <v>4185</v>
+        <v>4165</v>
       </c>
       <c r="N16" t="n">
         <v>0.95</v>
       </c>
       <c r="O16" t="n">
-        <v>22591146640</v>
+        <v>24098855437</v>
       </c>
       <c r="P16" t="n">
         <v>6900</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>STO 사업 추진 소식 및 미국 코인 주식거래 허용 호재 기대. 그러나 급락 및 경고 예고에 대한 우려도 존재.</t>
+          <t>미버스랩스의 STO 사업 추진과 미국 코인 주식거래 허용 이슈에 대한 기대감. 일부 공시 내용이 있으나, 감정적 표현과 확인 불가능한 전망이 다수 포함.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['STO', '암호화폐', '테마']</t>
+          <t>['STO', '암호화폐', '주식거래']</t>
         </is>
       </c>
       <c r="X16" t="n">

--- a/data/trending_integrated_20260918_10.xlsx
+++ b/data/trending_integrated_20260918_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8330</v>
+        <v>8450</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.66%</t>
+          <t>'+20.37%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.59</v>
       </c>
       <c r="O2" t="n">
-        <v>116611240340</v>
+        <v>120890640885</v>
       </c>
       <c r="P2" t="n">
         <v>16200</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>일부 투자자 손절 및 매도 의견 존재. 8,000원 안착 기대감.</t>
+          <t>매물대 저항 및 안착 실패 가능성 언급. 급등 후 차익 실현 및 관망세 짙어짐.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['매도 의견', '손절', '8000원 안착']</t>
+          <t>['매물대 저항', '차익 실현', '안착 실패']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24750</v>
+        <v>24700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.58%</t>
+          <t>'+14.35%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.2</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="H3" t="n">
         <v>2.41</v>
@@ -702,7 +702,7 @@
         <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>160988971575</v>
+        <v>170115947600</v>
       </c>
       <c r="P3" t="n">
         <v>59600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>박스권 상단 돌파 후 5~6만원대 재진입 및 25,000원 돌파 기대감. 통신주 테마 언급.</t>
+          <t>과거 고가 대비 현재 주가 매력 부각. 통신주 강세와 연계된 2차 VI 시도 및 박스권 상단 돌파 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['박스권 돌파', '통신주', '25000원 돌파']</t>
+          <t>['과거 고가', '통신주', '박스권 돌파']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13080</v>
+        <v>13100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.95%</t>
+          <t>'+13.13%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>179</v>
+        <v>230</v>
       </c>
       <c r="H4" t="n">
         <v>8.029999999999999</v>
@@ -794,7 +794,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>95306191175</v>
+        <v>98070917245</v>
       </c>
       <c r="P4" t="n">
         <v>21150</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>셀그램 관련 뉴스 기대감 있으나, 주가 변동성과 개인 손실 우려 제기.</t>
+          <t>셀그램 관련 뉴스 기대감 속 변동성 확대. 외인 매수세 유입 관찰되나, 단기 차익 실현 의견도 공존.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['셀그램', '뉴스 기대', '주가 변동성']</t>
+          <t>['셀그램', '외인 매수', '차익 실현']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6620</v>
+        <v>6580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.59%</t>
+          <t>'+11.90%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1.02</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H5" t="n">
         <v>2.85</v>
@@ -886,7 +886,7 @@
         <v>1.83</v>
       </c>
       <c r="O5" t="n">
-        <v>69273495875</v>
+        <v>72904148985</v>
       </c>
       <c r="P5" t="n">
         <v>11760</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가온전선과 비교하며 변압기 관련주로서의 상승 기대감 표시. 종가상승 가능성 언급.</t>
+          <t>변압기 관련주로서 1만원 이하 주가에 대한 저평가론. 차트상 상승 추세 및 추가 상장 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['변압기', '가온전선', '종가상승']</t>
+          <t>['변압기', '저평가론', '추가 상장']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17820</v>
+        <v>17920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.48%</t>
+          <t>'+11.10%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.27</v>
       </c>
       <c r="E6" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F6" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G6" t="n">
-        <v>958</v>
+        <v>1032</v>
       </c>
       <c r="H6" t="n">
         <v>4.61</v>
@@ -978,7 +978,7 @@
         <v>4.88</v>
       </c>
       <c r="O6" t="n">
-        <v>398755282540</v>
+        <v>415523511285</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>18,000원 돌파에 대한 기대감 고조. 광통신 관련 기업 주가 상승 소식.</t>
+          <t>높은 수익률 달성 및 숏커버링 발생으로 인한 급등 출발. 18,000원 돌파 및 20,000원 목표 기대감 형성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['18000원 돌파', '광통신', '공매도']</t>
+          <t>['수익률', '숏커버링', '18000원 돌파']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H7" t="n">
         <v>11.44</v>
@@ -1070,7 +1070,7 @@
         <v>11.46</v>
       </c>
       <c r="O7" t="n">
-        <v>116369328250</v>
+        <v>125814662225</v>
       </c>
       <c r="P7" t="n">
         <v>75900</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13960</v>
+        <v>13990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.55%</t>
+          <t>'+8.79%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H8" t="n">
         <v>2.83</v>
@@ -1162,7 +1162,7 @@
         <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>103359406970</v>
+        <v>110993535965</v>
       </c>
       <c r="P8" t="n">
         <v>20300</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>수조원 규모 미국 LA 전력청 투자 가능성 제기. 제품 테스트 완료 및 미주 매출 3.5배 폭증 소식.</t>
+          <t>미국 LA 전력청 납품 테스트 완료 및 미주 매출 3.5배 폭증 소식에 기대감 형성. 주가 135안착 여부에 관심 집중.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LA 전력청', '매출 폭증', '제품 테스트']</t>
+          <t>['LA전력청', '매출 폭증', '테스트 완료']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,79 +1207,79 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54400</v>
+        <v>19000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+6.46%</t>
+          <t>'+5.97%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.08</v>
+        <v>0.38</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>248</v>
+        <v>157</v>
       </c>
       <c r="H9" t="n">
-        <v>38.54</v>
+        <v>0.98</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>51100</v>
+        <v>17930</v>
       </c>
       <c r="K9" t="n">
-        <v>51600</v>
+        <v>18400</v>
       </c>
       <c r="L9" t="n">
-        <v>55200</v>
+        <v>20400</v>
       </c>
       <c r="M9" t="n">
-        <v>51500</v>
+        <v>17910</v>
       </c>
       <c r="N9" t="n">
-        <v>38.62</v>
+        <v>0.6</v>
       </c>
       <c r="O9" t="n">
-        <v>139070240950</v>
+        <v>60002366655</v>
       </c>
       <c r="P9" t="n">
-        <v>67300</v>
+        <v>21100</v>
       </c>
       <c r="Q9" t="n">
-        <v>23150</v>
+        <v>9900</v>
       </c>
       <c r="R9" t="n">
-        <v>403000</v>
+        <v>24000</v>
       </c>
       <c r="S9" t="n">
-        <v>59000</v>
+        <v>22000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외인·기관 매수세 유입에 따른 우상향 추세 전망. 52,000~53,000원 돌파 기대.</t>
+          <t>보호예수 물량 해제에 따른 주가 변동성 우려 속, 기술이전 기대감 및 긍정적 수급 분석.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인 매수', '우상향', '추세 전망']</t>
+          <t>['보호예수', '기술이전', '수급']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19530</v>
+        <v>54100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+5.62%</t>
+          <t>'+5.87%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>219</v>
+        <v>269</v>
       </c>
       <c r="H10" t="n">
-        <v>10.74</v>
+        <v>38.54</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18490</v>
+        <v>51100</v>
       </c>
       <c r="K10" t="n">
-        <v>18900</v>
+        <v>51600</v>
       </c>
       <c r="L10" t="n">
-        <v>19700</v>
+        <v>55200</v>
       </c>
       <c r="M10" t="n">
-        <v>18770</v>
+        <v>51500</v>
       </c>
       <c r="N10" t="n">
-        <v>10.85</v>
+        <v>38.62</v>
       </c>
       <c r="O10" t="n">
-        <v>71707022490</v>
+        <v>146144868350</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R10" t="n">
-        <v>213000</v>
+        <v>403000</v>
       </c>
       <c r="S10" t="n">
-        <v>66000</v>
+        <v>59000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 원전주 상승세 및 중동 전쟁 종전 기대감 속 주가 상승 전망. 대차해지 운동 참여 독려.</t>
+          <t>외인/기관 매수세 유입에 따른 우상향 추세 기대. 52,000원 돌파 및 53,000원 안착 여부에 관심 집중.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전주', '대차해지', '중동 전쟁']</t>
+          <t>['외인/기관 매수', '우상향', '52000원 돌파']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1823000</v>
+        <v>19430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.47%</t>
+          <t>'+5.08%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="E11" t="n">
-        <v>736</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>451</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>3089</v>
+        <v>236</v>
       </c>
       <c r="H11" t="n">
-        <v>50.1</v>
+        <v>10.74</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1745000</v>
+        <v>18490</v>
       </c>
       <c r="K11" t="n">
-        <v>1810000</v>
+        <v>18900</v>
       </c>
       <c r="L11" t="n">
-        <v>1828000</v>
+        <v>19700</v>
       </c>
       <c r="M11" t="n">
-        <v>1805000</v>
+        <v>18770</v>
       </c>
       <c r="N11" t="n">
-        <v>50.2</v>
+        <v>10.85</v>
       </c>
       <c r="O11" t="n">
-        <v>1416356941500</v>
+        <v>77271390355</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>333000</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>129000</v>
+        <v>213000</v>
       </c>
       <c r="S11" t="n">
-        <v>65000</v>
+        <v>66000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 증시 및 반도체주 급등에 따른 200만 돌파 기대. 공급 부족 장기화 전망 및 AI 두뇌 역할 강조.</t>
+          <t>미국 증시 원전주 강세 및 중동 전쟁 종전 기대감에 따른 하반기 상승 전망. 소액주주들의 대차해지 운동 동참 촉구.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '공급 부족']</t>
+          <t>['원전주', '대차해지', '하반기 전망']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18730</v>
+        <v>13980</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.46%</t>
+          <t>'+4.64%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="G12" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="H12" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17930</v>
+        <v>13360</v>
       </c>
       <c r="K12" t="n">
-        <v>18400</v>
+        <v>13450</v>
       </c>
       <c r="L12" t="n">
-        <v>20400</v>
+        <v>14450</v>
       </c>
       <c r="M12" t="n">
-        <v>17910</v>
+        <v>13450</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>58712111425</v>
+        <v>24392827970</v>
       </c>
       <c r="P12" t="n">
-        <v>21100</v>
+        <v>19380</v>
       </c>
       <c r="Q12" t="n">
-        <v>9900</v>
+        <v>3200</v>
       </c>
       <c r="R12" t="n">
-        <v>24000</v>
+        <v>55000</v>
       </c>
       <c r="S12" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>보호예수 물량 해제에 따른 주가 변동성 우려 속, 기술이전 기대감 및 긍정적 수급 분석.</t>
+          <t>호남 반도체 사업 관련 기대감 속 실적 개선 가능성 언급. 2만원 목표 제시 및 차익 실현 의견 공존.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보호예수', '기술이전', '수급']</t>
+          <t>['호남 반도체', '실적 개선', '2만원 목표']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>259000</v>
+        <v>1821000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.57%</t>
+          <t>'+4.36%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>762</v>
       </c>
       <c r="F13" t="n">
-        <v>483</v>
+        <v>458</v>
       </c>
       <c r="G13" t="n">
-        <v>2562</v>
+        <v>3137</v>
       </c>
       <c r="H13" t="n">
-        <v>46.48</v>
+        <v>50.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>252500</v>
+        <v>1745000</v>
       </c>
       <c r="K13" t="n">
-        <v>261000</v>
+        <v>1810000</v>
       </c>
       <c r="L13" t="n">
-        <v>261000</v>
+        <v>1828000</v>
       </c>
       <c r="M13" t="n">
-        <v>258000</v>
+        <v>1805000</v>
       </c>
       <c r="N13" t="n">
-        <v>46.52</v>
+        <v>50.2</v>
       </c>
       <c r="O13" t="n">
-        <v>812784412000</v>
+        <v>1513289653000</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>78600</v>
+        <v>333000</v>
       </c>
       <c r="R13" t="n">
-        <v>-509000</v>
+        <v>129000</v>
       </c>
       <c r="S13" t="n">
-        <v>226000</v>
+        <v>65000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈 언급되며 주가 하락 우려 제기. 미국 국채 금리 하락 소식.</t>
+          <t>미국 증시 및 반도체주 급등에 따른 200만 돌파 기대. 공급 부족 장기화 전망 및 AI 두뇌 역할 강조.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '국채 금리', '주가 조작']</t>
+          <t>['반도체', 'AI', '공급 부족']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17540</v>
+        <v>259000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.68%</t>
+          <t>'+2.57%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.27</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>492</v>
       </c>
       <c r="G14" t="n">
-        <v>103</v>
+        <v>2150</v>
       </c>
       <c r="H14" t="n">
-        <v>0.97</v>
+        <v>46.48</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>17250</v>
+        <v>252500</v>
       </c>
       <c r="K14" t="n">
-        <v>17920</v>
+        <v>261000</v>
       </c>
       <c r="L14" t="n">
-        <v>18440</v>
+        <v>261000</v>
       </c>
       <c r="M14" t="n">
-        <v>17450</v>
+        <v>258000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7</v>
+        <v>46.52</v>
       </c>
       <c r="O14" t="n">
-        <v>62712651335</v>
+        <v>871118985500</v>
       </c>
       <c r="P14" t="n">
-        <v>30550</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>6100</v>
+        <v>78600</v>
       </c>
       <c r="R14" t="n">
-        <v>-82000</v>
+        <v>-509000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>226000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 증시 양자컴퓨터 및 보안 관련주 급등에 따른 엑스게이트의 상승 기대. AI, 반도체, 양자컴퓨터 테마 언급. 객관적 근거보다는 시장 분위기에 편승.</t>
+          <t>글로벌 경제 불확실성 속 금리 하락 뉴스에도 주가 상승 기대감은 제한적. 정치적 이슈 언급 다수.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보안', 'AI']</t>
+          <t>['금리 하락', '정치 이슈', '주가 상승 기대']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>85500</v>
+        <v>17510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+1.51%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>0.27</v>
       </c>
       <c r="E15" t="n">
-        <v>149</v>
+        <v>62</v>
       </c>
       <c r="F15" t="n">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
-        <v>771</v>
+        <v>107</v>
       </c>
       <c r="H15" t="n">
-        <v>23.23</v>
+        <v>0.97</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>85400</v>
+        <v>17250</v>
       </c>
       <c r="K15" t="n">
-        <v>87300</v>
+        <v>17920</v>
       </c>
       <c r="L15" t="n">
-        <v>87800</v>
+        <v>18440</v>
       </c>
       <c r="M15" t="n">
-        <v>85300</v>
+        <v>17450</v>
       </c>
       <c r="N15" t="n">
-        <v>23.27</v>
+        <v>0.7</v>
       </c>
       <c r="O15" t="n">
-        <v>59504065750</v>
+        <v>64322096225</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>30550</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>6100</v>
       </c>
       <c r="R15" t="n">
-        <v>-105000</v>
+        <v>-82000</v>
       </c>
       <c r="S15" t="n">
-        <v>-48000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 증시 원전주 급등 및 한미 외교장관 회담 계기 대미 투자 관련 발표 가능성 언급. 에너지 관리, GPU 전력 부족 뉴스와 연계. 일부 뉴스 기반.</t>
+          <t>미국 양자컴퓨터 주식 아이온큐 급등 소식에 연관 종목 동반 상승 기대감 형성. 다만, 명확한 팩트 기반 분석보다는 기대감 위주 논의.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원자력', '대미투자', '에너지']</t>
+          <t>['양자컴퓨터', '보안주', 'AI 반도체']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,97 +1844,189 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4185</v>
+        <v>85900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-9.71%</t>
+          <t>'+0.59%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.4</v>
+        <v>-0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="F16" t="n">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="G16" t="n">
-        <v>559</v>
+        <v>802</v>
       </c>
       <c r="H16" t="n">
-        <v>0.55</v>
+        <v>23.23</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4635</v>
+        <v>85400</v>
       </c>
       <c r="K16" t="n">
-        <v>4465</v>
+        <v>87300</v>
       </c>
       <c r="L16" t="n">
-        <v>4535</v>
+        <v>87800</v>
       </c>
       <c r="M16" t="n">
-        <v>4165</v>
+        <v>85300</v>
       </c>
       <c r="N16" t="n">
-        <v>0.95</v>
+        <v>23.27</v>
       </c>
       <c r="O16" t="n">
-        <v>24098855437</v>
+        <v>64163670250</v>
       </c>
       <c r="P16" t="n">
-        <v>6900</v>
+        <v>139200</v>
       </c>
       <c r="Q16" t="n">
-        <v>1738</v>
+        <v>57000</v>
       </c>
       <c r="R16" t="n">
-        <v>60000</v>
+        <v>-105000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미버스랩스의 STO 사업 추진과 미국 코인 주식거래 허용 이슈에 대한 기대감. 일부 공시 내용이 있으나, 감정적 표현과 확인 불가능한 전망이 다수 포함.</t>
+          <t>미국 증시 원전주 급등 및 한미 외교장관 회담 계기 대미 투자 관련 발표 가능성 언급. 에너지 관리, GPU 전력 부족 뉴스와 연계. 일부 뉴스 기반.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['원자력', '대미투자', '에너지']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4270</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>'-7.87%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>132</v>
+      </c>
+      <c r="F17" t="n">
+        <v>83</v>
+      </c>
+      <c r="G17" t="n">
+        <v>574</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>4635</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4465</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4535</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4165</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O17" t="n">
+        <v>25957301732</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6900</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1738</v>
+      </c>
+      <c r="R17" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>미버스랩스의 STO 사업 추진과 미국 코인 주식거래 허용 이슈에 대한 기대감. 일부 공시 내용이 있으나, 감정적 표현과 확인 불가능한 전망이 다수 포함.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
         <v>0.3</v>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>['STO', '암호화폐', '주식거래']</t>
         </is>
       </c>
-      <c r="X16" t="n">
+      <c r="X17" t="n">
         <v>3</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>201490</t>
         </is>

--- a/data/trending_integrated_20260918_10.xlsx
+++ b/data/trending_integrated_20260918_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>8330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.37%</t>
+          <t>'+18.66%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.59</v>
       </c>
       <c r="O2" t="n">
-        <v>120890640885</v>
+        <v>123542835675</v>
       </c>
       <c r="P2" t="n">
         <v>16200</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>매물대 저항 및 안착 실패 가능성 언급. 급등 후 차익 실현 및 관망세 짙어짐.</t>
+          <t>매물대 부담 및 지속적인 하락 추세 경고. 8000원 안착 시 긍정적 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['매물대 저항', '차익 실현', '안착 실패']</t>
+          <t>['매물대 부담', '하락 추세', '8000 안착']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24700</v>
+        <v>24800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.35%</t>
+          <t>'+14.81%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.2</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H3" t="n">
         <v>2.41</v>
@@ -702,7 +702,7 @@
         <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>170115947600</v>
+        <v>177811930675</v>
       </c>
       <c r="P3" t="n">
         <v>59600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>과거 고가 대비 현재 주가 매력 부각. 통신주 강세와 연계된 2차 VI 시도 및 박스권 상단 돌파 기대.</t>
+          <t>주가 박스권 상단 돌파 시도 및 25,000원 목표 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['과거 고가', '통신주', '박스권 돌파']</t>
+          <t>['박스권', '돌파', '목표가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13100</v>
+        <v>12990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.13%</t>
+          <t>'+12.18%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="H4" t="n">
         <v>8.029999999999999</v>
@@ -794,7 +794,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>98070917245</v>
+        <v>101449969190</v>
       </c>
       <c r="P4" t="n">
         <v>21150</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>셀그램 관련 뉴스 기대감 속 변동성 확대. 외인 매수세 유입 관찰되나, 단기 차익 실현 의견도 공존.</t>
+          <t>셀그램 관련 뉴스 기대감에도 불구하고 프로그램 매수세 증가와 함께 변동성 확대. 2030년까지의 장기적 관점 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['셀그램', '외인 매수', '차익 실현']</t>
+          <t>['셀그램', '프로그램 매수', '장기 전망']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6580</v>
+        <v>17940</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.90%</t>
+          <t>'+11.22%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>-0.27</v>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>1103</v>
       </c>
       <c r="H5" t="n">
-        <v>2.85</v>
+        <v>4.61</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5880</v>
+        <v>16130</v>
       </c>
       <c r="K5" t="n">
-        <v>5950</v>
+        <v>16360</v>
       </c>
       <c r="L5" t="n">
-        <v>6920</v>
+        <v>18230</v>
       </c>
       <c r="M5" t="n">
-        <v>5840</v>
+        <v>16170</v>
       </c>
       <c r="N5" t="n">
-        <v>1.83</v>
+        <v>4.88</v>
       </c>
       <c r="O5" t="n">
-        <v>72904148985</v>
+        <v>440254403480</v>
       </c>
       <c r="P5" t="n">
-        <v>11760</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>1620</v>
+        <v>1272</v>
       </c>
       <c r="R5" t="n">
-        <v>900000</v>
+        <v>474000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>변압기 관련주로서 1만원 이하 주가에 대한 저평가론. 차트상 상승 추세 및 추가 상장 가능성 언급.</t>
+          <t>수익률 520% 돌파 및 외인 기관 투신 매수세 급증. 18000원 돌파 및 20000원 목표.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['변압기', '저평가론', '추가 상장']</t>
+          <t>['수익률 520%', '외인 기관 매수', '18000 돌파']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17920</v>
+        <v>6540</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.10%</t>
+          <t>'+11.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.27</v>
+        <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>158</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>1032</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>4.61</v>
+        <v>2.85</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>16130</v>
+        <v>5880</v>
       </c>
       <c r="K6" t="n">
-        <v>16360</v>
+        <v>5950</v>
       </c>
       <c r="L6" t="n">
-        <v>18230</v>
+        <v>6920</v>
       </c>
       <c r="M6" t="n">
-        <v>16170</v>
+        <v>5840</v>
       </c>
       <c r="N6" t="n">
-        <v>4.88</v>
+        <v>1.83</v>
       </c>
       <c r="O6" t="n">
-        <v>415523511285</v>
+        <v>75137055585</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>11760</v>
       </c>
       <c r="Q6" t="n">
-        <v>1272</v>
+        <v>1620</v>
       </c>
       <c r="R6" t="n">
-        <v>474000</v>
+        <v>900000</v>
       </c>
       <c r="S6" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>높은 수익률 달성 및 숏커버링 발생으로 인한 급등 출발. 18,000원 돌파 및 20,000원 목표 기대감 형성.</t>
+          <t>변압기 주식 관련 긍정적 언급과 함께 매도세 급증 및 윗꼬리 발생. 최대 이익 공시 후 주가 하락.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['수익률', '숏커버링', '18000원 돌파']</t>
+          <t>['변압기 주식', '매도세 급증', '최대 이익 공시']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31250</v>
+        <v>31000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.42%</t>
+          <t>'+9.54%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="H7" t="n">
         <v>11.44</v>
@@ -1070,7 +1070,7 @@
         <v>11.46</v>
       </c>
       <c r="O7" t="n">
-        <v>125814662225</v>
+        <v>132194816100</v>
       </c>
       <c r="P7" t="n">
         <v>75900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 언급되며 상승 기대감 존재. 구리 490억원 매수 소식.</t>
+          <t>가온전선 대비 상대적 움직임 약세. 36,000원 돌파 시 본격 상승 구간 진입 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['구리 매수', '전선주', '상승 기대']</t>
+          <t>['가온전선 비교', '상승 구간', '돌파 시도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13990</v>
+        <v>13930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.79%</t>
+          <t>'+8.32%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H8" t="n">
         <v>2.83</v>
@@ -1162,7 +1162,7 @@
         <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>110993535965</v>
+        <v>114817378200</v>
       </c>
       <c r="P8" t="n">
         <v>20300</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 LA 전력청 납품 테스트 완료 및 미주 매출 3.5배 폭증 소식에 기대감 형성. 주가 135안착 여부에 관심 집중.</t>
+          <t>미주 매출 3.5배 폭증 및 LA전력청 수주 기대감. 전선·전력설비 테마 강세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LA전력청', '매출 폭증', '테스트 완료']</t>
+          <t>['LA전력청', '미주 매출', '전선 테마']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19000</v>
+        <v>18920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.97%</t>
+          <t>'+5.52%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.38</v>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F9" t="n">
         <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H9" t="n">
         <v>0.98</v>
@@ -1254,7 +1254,7 @@
         <v>0.6</v>
       </c>
       <c r="O9" t="n">
-        <v>60002366655</v>
+        <v>61197646290</v>
       </c>
       <c r="P9" t="n">
         <v>21100</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54100</v>
+        <v>53600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+5.87%</t>
+          <t>'+4.89%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="H10" t="n">
         <v>38.54</v>
@@ -1346,7 +1346,7 @@
         <v>38.62</v>
       </c>
       <c r="O10" t="n">
-        <v>146144868350</v>
+        <v>153241214450</v>
       </c>
       <c r="P10" t="n">
         <v>67300</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외인/기관 매수세 유입에 따른 우상향 추세 기대. 52,000원 돌파 및 53,000원 안착 여부에 관심 집중.</t>
+          <t>외인 기관 매수세 유입 및 개인 매도세 속 우상향 추세 전망. 52000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외인/기관 매수', '우상향', '52000원 돌파']</t>
+          <t>['외인 기관 매수', '우상향', '52000 돌파']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19430</v>
+        <v>1818000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+5.08%</t>
+          <t>'+4.18%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>789</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>469</v>
       </c>
       <c r="G11" t="n">
-        <v>236</v>
+        <v>3194</v>
       </c>
       <c r="H11" t="n">
-        <v>10.74</v>
+        <v>50.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18490</v>
+        <v>1745000</v>
       </c>
       <c r="K11" t="n">
-        <v>18900</v>
+        <v>1810000</v>
       </c>
       <c r="L11" t="n">
-        <v>19700</v>
+        <v>1828000</v>
       </c>
       <c r="M11" t="n">
-        <v>18770</v>
+        <v>1805000</v>
       </c>
       <c r="N11" t="n">
-        <v>10.85</v>
+        <v>50.2</v>
       </c>
       <c r="O11" t="n">
-        <v>77271390355</v>
+        <v>1635159159000</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>333000</v>
       </c>
       <c r="R11" t="n">
-        <v>213000</v>
+        <v>129000</v>
       </c>
       <c r="S11" t="n">
-        <v>66000</v>
+        <v>65000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 증시 원전주 강세 및 중동 전쟁 종전 기대감에 따른 하반기 상승 전망. 소액주주들의 대차해지 운동 동참 촉구.</t>
+          <t>미국 증시 및 반도체주 급등에 따른 200만 돌파 기대. 공급 부족 장기화 전망 및 AI 두뇌 역할 강조.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전주', '대차해지', '하반기 전망']</t>
+          <t>['반도체', 'AI', '공급 부족']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13980</v>
+        <v>13910</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.64%</t>
+          <t>'+4.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>24392827970</v>
+        <v>25990643935</v>
       </c>
       <c r="P12" t="n">
         <v>19380</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>호남 반도체 사업 관련 기대감 속 실적 개선 가능성 언급. 2만원 목표 제시 및 차익 실현 의견 공존.</t>
+          <t>호남반도체 속행 및 실적 개선 기대감. 2만원 목표 제시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['호남 반도체', '실적 개선', '2만원 목표']</t>
+          <t>['호남반도체', '실적 개선', '2만원 목표']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1821000</v>
+        <v>19250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+4.36%</t>
+          <t>'+4.11%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>762</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
-        <v>458</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>3137</v>
+        <v>259</v>
       </c>
       <c r="H13" t="n">
-        <v>50.1</v>
+        <v>10.74</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1745000</v>
+        <v>18490</v>
       </c>
       <c r="K13" t="n">
-        <v>1810000</v>
+        <v>18900</v>
       </c>
       <c r="L13" t="n">
-        <v>1828000</v>
+        <v>19700</v>
       </c>
       <c r="M13" t="n">
-        <v>1805000</v>
+        <v>18770</v>
       </c>
       <c r="N13" t="n">
-        <v>50.2</v>
+        <v>10.85</v>
       </c>
       <c r="O13" t="n">
-        <v>1513289653000</v>
+        <v>81811155300</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>333000</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>129000</v>
+        <v>213000</v>
       </c>
       <c r="S13" t="n">
-        <v>65000</v>
+        <v>66000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 증시 및 반도체주 급등에 따른 200만 돌파 기대. 공급 부족 장기화 전망 및 AI 두뇌 역할 강조.</t>
+          <t>미국장 원전주 상승세 및 중동 전쟁 종전 논의 속 하반기 상승 기대. 대차해지 운동 동참 촉구.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '공급 부족']</t>
+          <t>['원전주', '대차해지', '하반기 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>259000</v>
+        <v>258000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.57%</t>
+          <t>'+2.18%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G14" t="n">
-        <v>2150</v>
+        <v>1854</v>
       </c>
       <c r="H14" t="n">
         <v>46.48</v>
@@ -1714,7 +1714,7 @@
         <v>46.52</v>
       </c>
       <c r="O14" t="n">
-        <v>871118985500</v>
+        <v>909841884250</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>글로벌 경제 불확실성 속 금리 하락 뉴스에도 주가 상승 기대감은 제한적. 정치적 이슈 언급 다수.</t>
+          <t>미국 국채 금리 하락 및 엔비디아 칩 판매량 증가 전망에 따른 반도체 업종 기대감. 40만 전자 목표.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['금리 하락', '정치 이슈', '주가 상승 기대']</t>
+          <t>['국채 금리', '엔비디아', '반도체 업종']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17510</v>
+        <v>17580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.51%</t>
+          <t>'+1.91%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.27</v>
       </c>
       <c r="E15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H15" t="n">
         <v>0.97</v>
@@ -1806,7 +1806,7 @@
         <v>0.7</v>
       </c>
       <c r="O15" t="n">
-        <v>64322096225</v>
+        <v>65227889865</v>
       </c>
       <c r="P15" t="n">
         <v>30550</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터 주식 아이온큐 급등 소식에 연관 종목 동반 상승 기대감 형성. 다만, 명확한 팩트 기반 분석보다는 기대감 위주 논의.</t>
+          <t>미국 양자컴퓨터 주식 급등에 따른 연관성 기대감 및 보안 관련주 동반 상승 가능성. 18,000원 돌파 및 신고가 예약 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보안주', 'AI 반도체']</t>
+          <t>['양자컴퓨터', '보안', '신고가']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85900</v>
+        <v>85800</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.59%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F16" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G16" t="n">
-        <v>802</v>
+        <v>815</v>
       </c>
       <c r="H16" t="n">
         <v>23.23</v>
@@ -1898,7 +1898,7 @@
         <v>23.27</v>
       </c>
       <c r="O16" t="n">
-        <v>64163670250</v>
+        <v>67592469500</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 증시 원전주 급등 및 한미 외교장관 회담 계기 대미 투자 관련 발표 가능성 언급. 에너지 관리, GPU 전력 부족 뉴스와 연계. 일부 뉴스 기반.</t>
+          <t>미국 증시 원전주 급등에 따른 국내 원전주 동반 상승 기대감. 대미 투자 관련 발표 가능성 및 120일선 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원자력', '대미투자', '에너지']</t>
+          <t>['원전주', '대미투자', '120일선']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4270</v>
+        <v>4250</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.87%</t>
+          <t>'-8.31%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.4</v>
       </c>
       <c r="E17" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="F17" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G17" t="n">
-        <v>574</v>
+        <v>601</v>
       </c>
       <c r="H17" t="n">
         <v>0.55</v>
@@ -1990,7 +1990,7 @@
         <v>0.95</v>
       </c>
       <c r="O17" t="n">
-        <v>25957301732</v>
+        <v>27075590909</v>
       </c>
       <c r="P17" t="n">
         <v>6900</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미버스랩스의 STO 사업 추진과 미국 코인 주식거래 허용 이슈에 대한 기대감. 일부 공시 내용이 있으나, 감정적 표현과 확인 불가능한 전망이 다수 포함.</t>
+          <t>계열사 STO 사업 추진 및 미국 코인 관련 주식 거래 허용 호재 기대, 그러나 공매도 및 경고 예고로 인한 부정적 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['STO', '암호화폐', '주식거래']</t>
+          <t>['STO', '코인', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2029,6 +2029,98 @@
       <c r="Z17" t="inlineStr">
         <is>
           <t>201490</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>원풍물산</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>30</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-30.23%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" t="n">
+        <v>94</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>43</v>
+      </c>
+      <c r="K18" t="n">
+        <v>44</v>
+      </c>
+      <c r="L18" t="n">
+        <v>44</v>
+      </c>
+      <c r="M18" t="n">
+        <v>26</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O18" t="n">
+        <v>90362757</v>
+      </c>
+      <c r="P18" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>26</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-58000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>장외 거래 및 지분 보유+기술 개발 루머 기반 매수세 유입 기대, 그러나 급락 및 투자자 손실 우려.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['장외거래', '지분', '기술개발']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>008290</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260918_10.xlsx
+++ b/data/trending_integrated_20260918_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8330</v>
+        <v>8400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.66%</t>
+          <t>'+19.66%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.59</v>
       </c>
       <c r="O2" t="n">
-        <v>123542835675</v>
+        <v>125724157345</v>
       </c>
       <c r="P2" t="n">
         <v>16200</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>매물대 부담 및 지속적인 하락 추세 경고. 8000원 안착 시 긍정적 전망.</t>
+          <t>상한가 안착 및 10,000원 돌파 기대감 있으나, 매물대 저항 및 사기 주식이라는 부정적 평가 공존. 폭포수 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['매물대 부담', '하락 추세', '8000 안착']</t>
+          <t>['매물대', '사기 주식', '폭포수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24800</v>
+        <v>25100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.81%</t>
+          <t>'+16.20%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.2</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H3" t="n">
         <v>2.41</v>
@@ -702,7 +702,7 @@
         <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>177811930675</v>
+        <v>187163044950</v>
       </c>
       <c r="P3" t="n">
         <v>59600</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>주가 박스권 상단 돌파 시도 및 25,000원 목표 기대감.</t>
+          <t>통신주 하락 속 성호전자 박스권 상단 돌파 시도. 외국인 매수세 유입 및 목표가 25000원 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['박스권', '돌파', '목표가']</t>
+          <t>['박스권 돌파', '외국인 매수', '목표가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12990</v>
+        <v>12000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.18%</t>
+          <t>'+13.10%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.67</v>
+        <v>-0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>250</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>8.029999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11580</v>
+        <v>10610</v>
       </c>
       <c r="K4" t="n">
-        <v>12200</v>
+        <v>10730</v>
       </c>
       <c r="L4" t="n">
-        <v>13820</v>
+        <v>12390</v>
       </c>
       <c r="M4" t="n">
-        <v>12100</v>
+        <v>10510</v>
       </c>
       <c r="N4" t="n">
-        <v>8.699999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="O4" t="n">
-        <v>101449969190</v>
+        <v>76530342765</v>
       </c>
       <c r="P4" t="n">
-        <v>21150</v>
+        <v>14350</v>
       </c>
       <c r="Q4" t="n">
-        <v>8140</v>
+        <v>465</v>
       </c>
       <c r="R4" t="n">
-        <v>540000</v>
+        <v>39000</v>
       </c>
       <c r="S4" t="n">
-        <v>87000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>셀그램 관련 뉴스 기대감에도 불구하고 프로그램 매수세 증가와 함께 변동성 확대. 2030년까지의 장기적 관점 제시.</t>
+          <t>주포 및 프로그램 매수세 유입에 따른 폭등 기대감. 호남반도체 관련주로 언급되며 전기·전선주 장세 수혜 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['셀그램', '프로그램 매수', '장기 전망']</t>
+          <t>['주포', '프로그램 매수', '호남반도체']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17940</v>
+        <v>6610</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.22%</t>
+          <t>'+12.41%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.27</v>
+        <v>1.02</v>
       </c>
       <c r="E5" t="n">
-        <v>173</v>
+        <v>84</v>
       </c>
       <c r="F5" t="n">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>1103</v>
+        <v>81</v>
       </c>
       <c r="H5" t="n">
-        <v>4.61</v>
+        <v>2.85</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16130</v>
+        <v>5880</v>
       </c>
       <c r="K5" t="n">
-        <v>16360</v>
+        <v>5950</v>
       </c>
       <c r="L5" t="n">
-        <v>18230</v>
+        <v>6920</v>
       </c>
       <c r="M5" t="n">
-        <v>16170</v>
+        <v>5840</v>
       </c>
       <c r="N5" t="n">
-        <v>4.88</v>
+        <v>1.83</v>
       </c>
       <c r="O5" t="n">
-        <v>440254403480</v>
+        <v>76652298875</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>11760</v>
       </c>
       <c r="Q5" t="n">
-        <v>1272</v>
+        <v>1620</v>
       </c>
       <c r="R5" t="n">
-        <v>474000</v>
+        <v>900000</v>
       </c>
       <c r="S5" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>수익률 520% 돌파 및 외인 기관 투신 매수세 급증. 18000원 돌파 및 20000원 목표.</t>
+          <t>외국인 및 프로그램 매수세 유입과 박스권 돌파에 대한 기대감. 변압기 관련주로서의 가치 재평가 가능성 언급. 사상 최대 이익 공시 후 주가 하락 경험.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['수익률 520%', '외인 기관 매수', '18000 돌파']</t>
+          <t>['박스권 돌파', '변압기', '외국인 매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6540</v>
+        <v>18070</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.22%</t>
+          <t>'+12.03%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.02</v>
+        <v>-0.27</v>
       </c>
       <c r="E6" t="n">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>1208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.85</v>
+        <v>4.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5880</v>
+        <v>16130</v>
       </c>
       <c r="K6" t="n">
-        <v>5950</v>
+        <v>16360</v>
       </c>
       <c r="L6" t="n">
-        <v>6920</v>
+        <v>18230</v>
       </c>
       <c r="M6" t="n">
-        <v>5840</v>
+        <v>16170</v>
       </c>
       <c r="N6" t="n">
-        <v>1.83</v>
+        <v>4.88</v>
       </c>
       <c r="O6" t="n">
-        <v>75137055585</v>
+        <v>463455628760</v>
       </c>
       <c r="P6" t="n">
-        <v>11760</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>1620</v>
+        <v>1272</v>
       </c>
       <c r="R6" t="n">
-        <v>900000</v>
+        <v>474000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>변압기 주식 관련 긍정적 언급과 함께 매도세 급증 및 윗꼬리 발생. 최대 이익 공시 후 주가 하락.</t>
+          <t>외인·기관·투신 매수세 유입 및 숏커버링 발생에 따른 급등 기대감. 18,000원 돌파 및 25층 목표가 제시. 공매도에 대한 부정적 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['변압기 주식', '매도세 급증', '최대 이익 공시']</t>
+          <t>['외인 매수', '숏커버링', '목표가']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31000</v>
+        <v>12920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.54%</t>
+          <t>'+11.57%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>-0.67</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
-        <v>98</v>
+        <v>374</v>
       </c>
       <c r="H7" t="n">
-        <v>11.44</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>28300</v>
+        <v>11580</v>
       </c>
       <c r="K7" t="n">
-        <v>28850</v>
+        <v>12200</v>
       </c>
       <c r="L7" t="n">
-        <v>32050</v>
+        <v>13820</v>
       </c>
       <c r="M7" t="n">
-        <v>28550</v>
+        <v>12100</v>
       </c>
       <c r="N7" t="n">
-        <v>11.46</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>132194816100</v>
+        <v>103915131520</v>
       </c>
       <c r="P7" t="n">
-        <v>75900</v>
+        <v>21150</v>
       </c>
       <c r="Q7" t="n">
-        <v>15000</v>
+        <v>8140</v>
       </c>
       <c r="R7" t="n">
-        <v>228000</v>
+        <v>540000</v>
       </c>
       <c r="S7" t="n">
-        <v>5000</v>
+        <v>87000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>가온전선 대비 상대적 움직임 약세. 36,000원 돌파 시 본격 상승 구간 진입 기대.</t>
+          <t>셀그램 관련 뉴스 기대감 있으나, 손실 경험 및 외인 매도세에 대한 우려. 2030년까지 파미셀에 대한 긍정적 전망 일부.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['가온전선 비교', '상승 구간', '돌파 시도']</t>
+          <t>['셀그램', '뉴스', '손실']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13930</v>
+        <v>31200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.32%</t>
+          <t>'+10.25%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>2.83</v>
+        <v>11.44</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12860</v>
+        <v>28300</v>
       </c>
       <c r="K8" t="n">
-        <v>13020</v>
+        <v>28850</v>
       </c>
       <c r="L8" t="n">
-        <v>14230</v>
+        <v>32050</v>
       </c>
       <c r="M8" t="n">
-        <v>13000</v>
+        <v>28550</v>
       </c>
       <c r="N8" t="n">
-        <v>2.83</v>
+        <v>11.46</v>
       </c>
       <c r="O8" t="n">
-        <v>114817378200</v>
+        <v>138722620100</v>
       </c>
       <c r="P8" t="n">
-        <v>20300</v>
+        <v>75900</v>
       </c>
       <c r="Q8" t="n">
-        <v>2885</v>
+        <v>15000</v>
       </c>
       <c r="R8" t="n">
-        <v>169000</v>
+        <v>228000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미주 매출 3.5배 폭증 및 LA전력청 수주 기대감. 전선·전력설비 테마 강세.</t>
+          <t>가온전선과의 비교 언급 및 자체 상승 기대감. 지수·수급 동반 상승 구간 진입 가능성 및 전선주로서의 강세 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LA전력청', '미주 매출', '전선 테마']</t>
+          <t>['가온전선', '수급', '전선주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18920</v>
+        <v>13940</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.52%</t>
+          <t>'+8.40%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="H9" t="n">
-        <v>0.98</v>
+        <v>2.83</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17930</v>
+        <v>12860</v>
       </c>
       <c r="K9" t="n">
-        <v>18400</v>
+        <v>13020</v>
       </c>
       <c r="L9" t="n">
-        <v>20400</v>
+        <v>14230</v>
       </c>
       <c r="M9" t="n">
-        <v>17910</v>
+        <v>13000</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6</v>
+        <v>2.83</v>
       </c>
       <c r="O9" t="n">
-        <v>61197646290</v>
+        <v>117297685985</v>
       </c>
       <c r="P9" t="n">
-        <v>21100</v>
+        <v>20300</v>
       </c>
       <c r="Q9" t="n">
-        <v>9900</v>
+        <v>2885</v>
       </c>
       <c r="R9" t="n">
-        <v>24000</v>
+        <v>169000</v>
       </c>
       <c r="S9" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>보호예수 물량 해제에 따른 주가 변동성 우려 속, 기술이전 기대감 및 긍정적 수급 분석.</t>
+          <t>미국 LA 전력청 납품 가능성 및 미주 매출 3.5배 폭증에 대한 기대감. 전선·전력설비 테마 섹터 주도 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보호예수', '기술이전', '수급']</t>
+          <t>['LA 전력청', '매출 폭증', '전력 설비']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -1314,13 +1314,13 @@
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="H10" t="n">
         <v>38.54</v>
@@ -1346,7 +1346,7 @@
         <v>38.62</v>
       </c>
       <c r="O10" t="n">
-        <v>153241214450</v>
+        <v>156320300450</v>
       </c>
       <c r="P10" t="n">
         <v>67300</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1818000</v>
+        <v>14000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+4.79%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>789</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>469</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>3194</v>
+        <v>180</v>
       </c>
       <c r="H11" t="n">
-        <v>50.1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1745000</v>
+        <v>13360</v>
       </c>
       <c r="K11" t="n">
-        <v>1810000</v>
+        <v>13450</v>
       </c>
       <c r="L11" t="n">
-        <v>1828000</v>
+        <v>14450</v>
       </c>
       <c r="M11" t="n">
-        <v>1805000</v>
+        <v>13450</v>
       </c>
       <c r="N11" t="n">
-        <v>50.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1635159159000</v>
+        <v>27404937395</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>19380</v>
       </c>
       <c r="Q11" t="n">
-        <v>333000</v>
+        <v>3200</v>
       </c>
       <c r="R11" t="n">
-        <v>129000</v>
+        <v>55000</v>
       </c>
       <c r="S11" t="n">
-        <v>65000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 증시 및 반도체주 급등에 따른 200만 돌파 기대. 공급 부족 장기화 전망 및 AI 두뇌 역할 강조.</t>
+          <t>호남반도체 관련 기대감 있으나, 실적 부진 및 급락 가능성에 대한 경고. 금호전기와의 비교 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '공급 부족']</t>
+          <t>['호남반도체', '실적', '급락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13910</v>
+        <v>18780</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.12%</t>
+          <t>'+4.74%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13360</v>
+        <v>17930</v>
       </c>
       <c r="K12" t="n">
-        <v>13450</v>
+        <v>18400</v>
       </c>
       <c r="L12" t="n">
-        <v>14450</v>
+        <v>20400</v>
       </c>
       <c r="M12" t="n">
-        <v>13450</v>
+        <v>17910</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O12" t="n">
-        <v>25990643935</v>
+        <v>62381220330</v>
       </c>
       <c r="P12" t="n">
-        <v>19380</v>
+        <v>21100</v>
       </c>
       <c r="Q12" t="n">
-        <v>3200</v>
+        <v>9900</v>
       </c>
       <c r="R12" t="n">
-        <v>55000</v>
+        <v>24000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>호남반도체 속행 및 실적 개선 기대감. 2만원 목표 제시.</t>
+          <t>보호예수 물량 해제에 따른 주가 변동성 우려 속, 기술이전 기대감 및 긍정적 수급 분석.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['호남반도체', '실적 개선', '2만원 목표']</t>
+          <t>['보호예수', '기술이전', '수급']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19250</v>
+        <v>1826000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+4.11%</t>
+          <t>'+4.64%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>69</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>471</v>
       </c>
       <c r="G13" t="n">
-        <v>259</v>
+        <v>3242</v>
       </c>
       <c r="H13" t="n">
-        <v>10.74</v>
+        <v>50.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18490</v>
+        <v>1745000</v>
       </c>
       <c r="K13" t="n">
-        <v>18900</v>
+        <v>1810000</v>
       </c>
       <c r="L13" t="n">
-        <v>19700</v>
+        <v>1828000</v>
       </c>
       <c r="M13" t="n">
-        <v>18770</v>
+        <v>1805000</v>
       </c>
       <c r="N13" t="n">
-        <v>10.85</v>
+        <v>50.2</v>
       </c>
       <c r="O13" t="n">
-        <v>81811155300</v>
+        <v>1752706164500</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>333000</v>
       </c>
       <c r="R13" t="n">
-        <v>213000</v>
+        <v>129000</v>
       </c>
       <c r="S13" t="n">
-        <v>66000</v>
+        <v>65000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국장 원전주 상승세 및 중동 전쟁 종전 논의 속 하반기 상승 기대. 대차해지 운동 동참 촉구.</t>
+          <t>미국 증시 및 반도체주 급등에 따른 200만 돌파 기대. 공급 부족 장기화 전망 및 AI 두뇌 역할 강조.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전주', '대차해지', '하반기 전망']</t>
+          <t>['반도체', 'AI', '공급 부족']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>258000</v>
+        <v>19270</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.18%</t>
+          <t>'+4.22%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.04</v>
+        <v>-0.11</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>80</v>
       </c>
       <c r="F14" t="n">
-        <v>491</v>
+        <v>53</v>
       </c>
       <c r="G14" t="n">
-        <v>1854</v>
+        <v>271</v>
       </c>
       <c r="H14" t="n">
-        <v>46.48</v>
+        <v>10.74</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>252500</v>
+        <v>18490</v>
       </c>
       <c r="K14" t="n">
-        <v>261000</v>
+        <v>18900</v>
       </c>
       <c r="L14" t="n">
-        <v>261000</v>
+        <v>19700</v>
       </c>
       <c r="M14" t="n">
-        <v>258000</v>
+        <v>18770</v>
       </c>
       <c r="N14" t="n">
-        <v>46.52</v>
+        <v>10.85</v>
       </c>
       <c r="O14" t="n">
-        <v>909841884250</v>
+        <v>84506803715</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>78600</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-509000</v>
+        <v>213000</v>
       </c>
       <c r="S14" t="n">
-        <v>226000</v>
+        <v>66000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 국채 금리 하락 및 엔비디아 칩 판매량 증가 전망에 따른 반도체 업종 기대감. 40만 전자 목표.</t>
+          <t>미국 원전주 상승세 및 중동 전쟁 종전 논의에 따른 기대감. 대차해지 운동 참여 독려 및 하반기 상승 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['국채 금리', '엔비디아', '반도체 업종']</t>
+          <t>['원전주', '대차해지', '하반기 전망']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17580</v>
+        <v>259000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.91%</t>
+          <t>'+2.57%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.27</v>
+        <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>482</v>
       </c>
       <c r="G15" t="n">
-        <v>112</v>
+        <v>1700</v>
       </c>
       <c r="H15" t="n">
-        <v>0.97</v>
+        <v>46.48</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17250</v>
+        <v>252500</v>
       </c>
       <c r="K15" t="n">
-        <v>17920</v>
+        <v>261000</v>
       </c>
       <c r="L15" t="n">
-        <v>18440</v>
+        <v>261000</v>
       </c>
       <c r="M15" t="n">
-        <v>17450</v>
+        <v>257500</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7</v>
+        <v>46.52</v>
       </c>
       <c r="O15" t="n">
-        <v>65227889865</v>
+        <v>1006476322750</v>
       </c>
       <c r="P15" t="n">
-        <v>30550</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>6100</v>
+        <v>78600</v>
       </c>
       <c r="R15" t="n">
-        <v>-82000</v>
+        <v>-509000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>226000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터 주식 급등에 따른 연관성 기대감 및 보안 관련주 동반 상승 가능성. 18,000원 돌파 및 신고가 예약 언급.</t>
+          <t>엔비디아 칩 판매량 증가 뉴스에도 불구하고, 정치적 이슈 및 시장 전반의 약세에 대한 언급. 주가 상승에 대한 불확실성 존재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보안', '신고가']</t>
+          <t>['엔비디아', '반도체', '주가 상승']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85800</v>
+        <v>17570</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+1.86%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.04</v>
+        <v>0.27</v>
       </c>
       <c r="E16" t="n">
-        <v>164</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="G16" t="n">
-        <v>815</v>
+        <v>117</v>
       </c>
       <c r="H16" t="n">
-        <v>23.23</v>
+        <v>0.97</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>85400</v>
+        <v>17250</v>
       </c>
       <c r="K16" t="n">
-        <v>87300</v>
+        <v>17920</v>
       </c>
       <c r="L16" t="n">
-        <v>87800</v>
+        <v>18440</v>
       </c>
       <c r="M16" t="n">
-        <v>85300</v>
+        <v>17450</v>
       </c>
       <c r="N16" t="n">
-        <v>23.27</v>
+        <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>67592469500</v>
+        <v>65778626425</v>
       </c>
       <c r="P16" t="n">
-        <v>139200</v>
+        <v>30550</v>
       </c>
       <c r="Q16" t="n">
-        <v>57000</v>
+        <v>6100</v>
       </c>
       <c r="R16" t="n">
-        <v>-105000</v>
+        <v>-82000</v>
       </c>
       <c r="S16" t="n">
-        <v>-48000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 증시 원전주 급등에 따른 국내 원전주 동반 상승 기대감. 대미 투자 관련 발표 가능성 및 120일선 돌파 가능성 언급.</t>
+          <t>미국 양자컴퓨터주 급등에 따른 엑스게이트 기대감. 단기 과열 및 매도 의견 상존.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전주', '대미투자', '120일선']</t>
+          <t>['양자컴퓨터', '보안주', '단기과열']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4250</v>
+        <v>85750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-8.31%</t>
+          <t>'+0.41%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.4</v>
+        <v>-0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="F17" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="G17" t="n">
-        <v>601</v>
+        <v>818</v>
       </c>
       <c r="H17" t="n">
-        <v>0.55</v>
+        <v>23.23</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4635</v>
+        <v>85400</v>
       </c>
       <c r="K17" t="n">
-        <v>4465</v>
+        <v>87300</v>
       </c>
       <c r="L17" t="n">
-        <v>4535</v>
+        <v>87800</v>
       </c>
       <c r="M17" t="n">
-        <v>4165</v>
+        <v>85300</v>
       </c>
       <c r="N17" t="n">
-        <v>0.95</v>
+        <v>23.27</v>
       </c>
       <c r="O17" t="n">
-        <v>27075590909</v>
+        <v>69232029800</v>
       </c>
       <c r="P17" t="n">
-        <v>6900</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>1738</v>
+        <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>60000</v>
+        <v>-105000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>계열사 STO 사업 추진 및 미국 코인 관련 주식 거래 허용 호재 기대, 그러나 공매도 및 경고 예고로 인한 부정적 전망.</t>
+          <t>미국 증시 원전주 급등에 따른 국내 원전주 동반 상승 기대감. 대미 투자 관련 발표 가능성 및 120일선 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['STO', '코인', '공매도']</t>
+          <t>['원전주', '대미투자', '120일선']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30</v>
+        <v>4245</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-30.23%</t>
+          <t>'-8.41%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.02</v>
+        <v>-0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="G18" t="n">
-        <v>94</v>
+        <v>629</v>
       </c>
       <c r="H18" t="n">
-        <v>3.69</v>
+        <v>0.55</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,58 +2067,150 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>43</v>
+        <v>4635</v>
       </c>
       <c r="K18" t="n">
-        <v>44</v>
+        <v>4465</v>
       </c>
       <c r="L18" t="n">
-        <v>44</v>
+        <v>4535</v>
       </c>
       <c r="M18" t="n">
-        <v>26</v>
+        <v>4165</v>
       </c>
       <c r="N18" t="n">
-        <v>3.71</v>
+        <v>0.95</v>
       </c>
       <c r="O18" t="n">
-        <v>90362757</v>
+        <v>27973253872</v>
       </c>
       <c r="P18" t="n">
-        <v>901</v>
+        <v>6900</v>
       </c>
       <c r="Q18" t="n">
-        <v>26</v>
+        <v>1738</v>
       </c>
       <c r="R18" t="n">
-        <v>-58000</v>
+        <v>60000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>장외 거래 및 지분 보유+기술 개발 루머 기반 매수세 유입 기대, 그러나 급락 및 투자자 손실 우려.</t>
+          <t>미버스랩스 STO 사업 추진 및 미국 코인 주식거래 허용 호재. 그러나 급락 및 공매도 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['STO', '암호화폐', '공매도']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>201490</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>원풍물산</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>30</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'-30.23%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E19" t="n">
+        <v>52</v>
+      </c>
+      <c r="F19" t="n">
+        <v>25</v>
+      </c>
+      <c r="G19" t="n">
+        <v>97</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>43</v>
+      </c>
+      <c r="K19" t="n">
+        <v>44</v>
+      </c>
+      <c r="L19" t="n">
+        <v>44</v>
+      </c>
+      <c r="M19" t="n">
+        <v>26</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O19" t="n">
+        <v>90362757</v>
+      </c>
+      <c r="P19" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>26</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-58000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>원풍물산, 장외거래 및 대주주 관련 언급. 기술 개발 기대감 있으나 급락 및 매도세 강함.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
         <v>0.2</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>['장외거래', '지분', '기술개발']</t>
-        </is>
-      </c>
-      <c r="X18" t="n">
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['장외거래', '기술 개발', '급락']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
         <v>2</v>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>008290</t>
         </is>

--- a/data/trending_integrated_20260918_10.xlsx
+++ b/data/trending_integrated_20260918_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8400</v>
+        <v>25850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.66%</t>
+          <t>'+19.68%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G2" t="n">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.41</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7020</v>
+        <v>21600</v>
       </c>
       <c r="K2" t="n">
-        <v>7180</v>
+        <v>22250</v>
       </c>
       <c r="L2" t="n">
-        <v>8890</v>
+        <v>25950</v>
       </c>
       <c r="M2" t="n">
-        <v>7150</v>
+        <v>21700</v>
       </c>
       <c r="N2" t="n">
-        <v>0.59</v>
+        <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>125724157345</v>
+        <v>208994878675</v>
       </c>
       <c r="P2" t="n">
-        <v>16200</v>
+        <v>59600</v>
       </c>
       <c r="Q2" t="n">
-        <v>1206</v>
+        <v>1030</v>
       </c>
       <c r="R2" t="n">
-        <v>574000</v>
+        <v>-241000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>상한가 안착 및 10,000원 돌파 기대감 있으나, 매물대 저항 및 사기 주식이라는 부정적 평가 공존. 폭포수 하락 가능성 언급.</t>
+          <t>외인 및 프로그램 매수세 유입과 함께 박스권 상단 돌파 시도. 통신주 테마 흐름 속에서 25,000원 목표 가격 제시. 과거 4~5만원대 경험 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['매물대', '사기 주식', '폭포수']</t>
+          <t>['박스권', '통신주', '외인매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25100</v>
+        <v>8330</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.20%</t>
+          <t>'+18.66%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>156</v>
+        <v>213</v>
       </c>
       <c r="H3" t="n">
-        <v>2.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>21600</v>
+        <v>7020</v>
       </c>
       <c r="K3" t="n">
-        <v>22250</v>
+        <v>7180</v>
       </c>
       <c r="L3" t="n">
-        <v>25150</v>
+        <v>8890</v>
       </c>
       <c r="M3" t="n">
-        <v>21700</v>
+        <v>7150</v>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>187163044950</v>
+        <v>128078689360</v>
       </c>
       <c r="P3" t="n">
-        <v>59600</v>
+        <v>16200</v>
       </c>
       <c r="Q3" t="n">
-        <v>1030</v>
+        <v>1206</v>
       </c>
       <c r="R3" t="n">
-        <v>-241000</v>
+        <v>574000</v>
       </c>
       <c r="S3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>통신주 하락 속 성호전자 박스권 상단 돌파 시도. 외국인 매수세 유입 및 목표가 25000원 언급.</t>
+          <t>상한가 안착 시 10,000원 돌파 기대감 있으나, 매물대 부담 및 전반적인 힘 부족으로 상승 여력 제한적. 사기 주식 논란도 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['박스권 돌파', '외국인 매수', '목표가']</t>
+          <t>['매물대', '상한가', '사기주식']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12000</v>
+        <v>18420</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.10%</t>
+          <t>'+14.20%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.1</v>
+        <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>147</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>1289</v>
       </c>
       <c r="H4" t="n">
-        <v>12.5</v>
+        <v>4.61</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>10610</v>
+        <v>16130</v>
       </c>
       <c r="K4" t="n">
-        <v>10730</v>
+        <v>16360</v>
       </c>
       <c r="L4" t="n">
-        <v>12390</v>
+        <v>18440</v>
       </c>
       <c r="M4" t="n">
-        <v>10510</v>
+        <v>16170</v>
       </c>
       <c r="N4" t="n">
-        <v>12.6</v>
+        <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>76530342765</v>
+        <v>499568927665</v>
       </c>
       <c r="P4" t="n">
-        <v>14350</v>
+        <v>31500</v>
       </c>
       <c r="Q4" t="n">
-        <v>465</v>
+        <v>1272</v>
       </c>
       <c r="R4" t="n">
-        <v>39000</v>
+        <v>474000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>주포 및 프로그램 매수세 유입에 따른 폭등 기대감. 호남반도체 관련주로 언급되며 전기·전선주 장세 수혜 전망.</t>
+          <t>외인·기관·투신 매수세 유입에 힘입어 18,000원 돌파 및 2차 매물대 공략 기대. 공매도 감소 및 숏커버링 발생 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주포', '프로그램 매수', '호남반도체']</t>
+          <t>['매수세', '공매도', '숏커버링']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6610</v>
+        <v>12930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.41%</t>
+          <t>'+11.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>-0.67</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="H5" t="n">
-        <v>2.85</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5880</v>
+        <v>11580</v>
       </c>
       <c r="K5" t="n">
-        <v>5950</v>
+        <v>12200</v>
       </c>
       <c r="L5" t="n">
-        <v>6920</v>
+        <v>13820</v>
       </c>
       <c r="M5" t="n">
-        <v>5840</v>
+        <v>12100</v>
       </c>
       <c r="N5" t="n">
-        <v>1.83</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>76652298875</v>
+        <v>106893125130</v>
       </c>
       <c r="P5" t="n">
-        <v>11760</v>
+        <v>21150</v>
       </c>
       <c r="Q5" t="n">
-        <v>1620</v>
+        <v>8140</v>
       </c>
       <c r="R5" t="n">
-        <v>900000</v>
+        <v>540000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외국인 및 프로그램 매수세 유입과 박스권 돌파에 대한 기대감. 변압기 관련주로서의 가치 재평가 가능성 언급. 사상 최대 이익 공시 후 주가 하락 경험.</t>
+          <t>셀그램 관련 뉴스 기대감 있으나, 주가는 하락 추세. 2030년까지 파미셀의 운이 트일 것이라는 긍정적 전망도 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['박스권 돌파', '변압기', '외국인 매수']</t>
+          <t>['셀그램', '뉴스', '기대감']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18070</v>
+        <v>11780</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.03%</t>
+          <t>'+11.03%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.27</v>
+        <v>-0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>189</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>134</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>1208</v>
+        <v>93</v>
       </c>
       <c r="H6" t="n">
-        <v>4.61</v>
+        <v>12.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>16130</v>
+        <v>10610</v>
       </c>
       <c r="K6" t="n">
-        <v>16360</v>
+        <v>10730</v>
       </c>
       <c r="L6" t="n">
-        <v>18230</v>
+        <v>12390</v>
       </c>
       <c r="M6" t="n">
-        <v>16170</v>
+        <v>10510</v>
       </c>
       <c r="N6" t="n">
-        <v>4.88</v>
+        <v>12.6</v>
       </c>
       <c r="O6" t="n">
-        <v>463455628760</v>
+        <v>82828095050</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>14350</v>
       </c>
       <c r="Q6" t="n">
-        <v>1272</v>
+        <v>465</v>
       </c>
       <c r="R6" t="n">
-        <v>474000</v>
+        <v>39000</v>
       </c>
       <c r="S6" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외인·기관·투신 매수세 유입 및 숏커버링 발생에 따른 급등 기대감. 18,000원 돌파 및 25층 목표가 제시. 공매도에 대한 부정적 언급.</t>
+          <t>주포 매수세 유입 및 호남반도체 관련 언급으로 상한가 기대감 형성. 전기·건설 테마주로 분류되며 프로그램 매수세 확인.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외인 매수', '숏커버링', '목표가']</t>
+          <t>['주포', '호남반도체', '상한가']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12920</v>
+        <v>31400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+11.57%</t>
+          <t>'+10.95%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.67</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="G7" t="n">
-        <v>374</v>
+        <v>104</v>
       </c>
       <c r="H7" t="n">
-        <v>8.029999999999999</v>
+        <v>11.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11580</v>
+        <v>28300</v>
       </c>
       <c r="K7" t="n">
-        <v>12200</v>
+        <v>28850</v>
       </c>
       <c r="L7" t="n">
-        <v>13820</v>
+        <v>32050</v>
       </c>
       <c r="M7" t="n">
-        <v>12100</v>
+        <v>28550</v>
       </c>
       <c r="N7" t="n">
-        <v>8.699999999999999</v>
+        <v>11.46</v>
       </c>
       <c r="O7" t="n">
-        <v>103915131520</v>
+        <v>142842446375</v>
       </c>
       <c r="P7" t="n">
-        <v>21150</v>
+        <v>75900</v>
       </c>
       <c r="Q7" t="n">
-        <v>8140</v>
+        <v>15000</v>
       </c>
       <c r="R7" t="n">
-        <v>540000</v>
+        <v>228000</v>
       </c>
       <c r="S7" t="n">
-        <v>87000</v>
+        <v>5000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>셀그램 관련 뉴스 기대감 있으나, 손실 경험 및 외인 매도세에 대한 우려. 2030년까지 파미셀에 대한 긍정적 전망 일부.</t>
+          <t>가온전선과의 비교 언급 속에서 대한전선 주가 상승 기대감. 지수 및 수급 호조에 따른 본격 상승 구간 진입 가능성 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['셀그램', '뉴스', '손실']</t>
+          <t>['가온전선', '상승', '수급']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,86 +1108,86 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31200</v>
+        <v>6510</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+10.25%</t>
+          <t>'+10.71%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02</v>
+        <v>1.02</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H8" t="n">
-        <v>11.44</v>
+        <v>2.85</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28300</v>
+        <v>5880</v>
       </c>
       <c r="K8" t="n">
-        <v>28850</v>
+        <v>5950</v>
       </c>
       <c r="L8" t="n">
-        <v>32050</v>
+        <v>6920</v>
       </c>
       <c r="M8" t="n">
-        <v>28550</v>
+        <v>5840</v>
       </c>
       <c r="N8" t="n">
-        <v>11.46</v>
+        <v>1.83</v>
       </c>
       <c r="O8" t="n">
-        <v>138722620100</v>
+        <v>77610140250</v>
       </c>
       <c r="P8" t="n">
-        <v>75900</v>
+        <v>11760</v>
       </c>
       <c r="Q8" t="n">
-        <v>15000</v>
+        <v>1620</v>
       </c>
       <c r="R8" t="n">
-        <v>228000</v>
+        <v>900000</v>
       </c>
       <c r="S8" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 언급 및 자체 상승 기대감. 지수·수급 동반 상승 구간 진입 가능성 및 전선주로서의 강세 전망.</t>
+          <t>변압기 테마 상승 기대감 속에 박스권 돌파 및 전환사채 발행 이슈. 외국인, 프로그램 매수세 유입 확인. 1만원 이하 변압기 주식 저평가 주장.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['가온전선', '수급', '전선주']</t>
+          <t>['변압기', '박스권', '전환사채']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13940</v>
+        <v>13920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.40%</t>
+          <t>'+8.24%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="H9" t="n">
         <v>2.83</v>
@@ -1254,7 +1254,7 @@
         <v>2.83</v>
       </c>
       <c r="O9" t="n">
-        <v>117297685985</v>
+        <v>119593104045</v>
       </c>
       <c r="P9" t="n">
         <v>20300</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 LA 전력청 납품 가능성 및 미주 매출 3.5배 폭증에 대한 기대감. 전선·전력설비 테마 섹터 주도 가능성 언급.</t>
+          <t>미주 매출 3.5배 폭증 및 제품 테스트 완료 소식 기반 수조원 미국 LA 전력청 계약 기대감. 전선·전력설비 테마주로 분류.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['LA 전력청', '매출 폭증', '전력 설비']</t>
+          <t>['LA전력청', '매출', '테스트']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,79 +1299,79 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53600</v>
+        <v>18760</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.89%</t>
+          <t>'+4.63%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.08</v>
+        <v>0.38</v>
       </c>
       <c r="E10" t="n">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
-        <v>291</v>
+        <v>184</v>
       </c>
       <c r="H10" t="n">
-        <v>38.54</v>
+        <v>0.98</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>51100</v>
+        <v>17930</v>
       </c>
       <c r="K10" t="n">
-        <v>51600</v>
+        <v>18400</v>
       </c>
       <c r="L10" t="n">
-        <v>55200</v>
+        <v>20400</v>
       </c>
       <c r="M10" t="n">
-        <v>51500</v>
+        <v>17910</v>
       </c>
       <c r="N10" t="n">
-        <v>38.62</v>
+        <v>0.6</v>
       </c>
       <c r="O10" t="n">
-        <v>156320300450</v>
+        <v>63597340175</v>
       </c>
       <c r="P10" t="n">
-        <v>67300</v>
+        <v>21100</v>
       </c>
       <c r="Q10" t="n">
-        <v>23150</v>
+        <v>9900</v>
       </c>
       <c r="R10" t="n">
-        <v>403000</v>
+        <v>24000</v>
       </c>
       <c r="S10" t="n">
-        <v>59000</v>
+        <v>22000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외인 기관 매수세 유입 및 개인 매도세 속 우상향 추세 전망. 52000원 돌파 기대.</t>
+          <t>회사의 잠재적 목표가 5만원 이상 제시 및 10만원 달성 가능성 언급. 보호예수 물량 해제 관련 우려와 기관/외인 매수세 유입에 대한 내용.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외인 기관 매수', '우상향', '52000 돌파']</t>
+          <t>['기술이전', '보호예수', '기관매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14000</v>
+        <v>1823000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.79%</t>
+          <t>'+4.47%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>471</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>3172</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>50.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13360</v>
+        <v>1745000</v>
       </c>
       <c r="K11" t="n">
-        <v>13450</v>
+        <v>1810000</v>
       </c>
       <c r="L11" t="n">
-        <v>14450</v>
+        <v>1828000</v>
       </c>
       <c r="M11" t="n">
-        <v>13450</v>
+        <v>1805000</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>50.2</v>
       </c>
       <c r="O11" t="n">
-        <v>27404937395</v>
+        <v>1839178808500</v>
       </c>
       <c r="P11" t="n">
-        <v>19380</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>3200</v>
+        <v>333000</v>
       </c>
       <c r="R11" t="n">
-        <v>55000</v>
+        <v>129000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>호남반도체 관련 기대감 있으나, 실적 부진 및 급락 가능성에 대한 경고. 금호전기와의 비교 언급.</t>
+          <t>미국 반도체 주식 및 필라델피아 반도체 지수 급등에 따른 SK하이닉스 상승 기대감. 내년도 예상 영업이익 증가 및 공급 부족 지속 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['호남반도체', '실적', '급락']</t>
+          <t>['AI', '반도체', '영업이익']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,86 +1476,86 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18780</v>
+        <v>53200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.74%</t>
+          <t>'+4.11%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.38</v>
+        <v>-0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>163</v>
+        <v>299</v>
       </c>
       <c r="H12" t="n">
-        <v>0.98</v>
+        <v>38.54</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17930</v>
+        <v>51100</v>
       </c>
       <c r="K12" t="n">
-        <v>18400</v>
+        <v>51600</v>
       </c>
       <c r="L12" t="n">
-        <v>20400</v>
+        <v>55200</v>
       </c>
       <c r="M12" t="n">
-        <v>17910</v>
+        <v>51500</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6</v>
+        <v>38.62</v>
       </c>
       <c r="O12" t="n">
-        <v>62381220330</v>
+        <v>160554570400</v>
       </c>
       <c r="P12" t="n">
-        <v>21100</v>
+        <v>67300</v>
       </c>
       <c r="Q12" t="n">
-        <v>9900</v>
+        <v>23150</v>
       </c>
       <c r="R12" t="n">
-        <v>24000</v>
+        <v>403000</v>
       </c>
       <c r="S12" t="n">
-        <v>22000</v>
+        <v>59000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>보호예수 물량 해제에 따른 주가 변동성 우려 속, 기술이전 기대감 및 긍정적 수급 분석.</t>
+          <t>외인 기관 매수세 유입 및 개인 매도세 속 우상향 추세 전망. 52000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보호예수', '기술이전', '수급']</t>
+          <t>['외인 기관 매수', '우상향', '52000 돌파']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1826000</v>
+        <v>19250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+4.64%</t>
+          <t>'+4.11%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>87</v>
       </c>
       <c r="F13" t="n">
-        <v>471</v>
+        <v>53</v>
       </c>
       <c r="G13" t="n">
-        <v>3242</v>
+        <v>275</v>
       </c>
       <c r="H13" t="n">
-        <v>50.1</v>
+        <v>10.74</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1745000</v>
+        <v>18490</v>
       </c>
       <c r="K13" t="n">
-        <v>1810000</v>
+        <v>18900</v>
       </c>
       <c r="L13" t="n">
-        <v>1828000</v>
+        <v>19700</v>
       </c>
       <c r="M13" t="n">
-        <v>1805000</v>
+        <v>18770</v>
       </c>
       <c r="N13" t="n">
-        <v>50.2</v>
+        <v>10.85</v>
       </c>
       <c r="O13" t="n">
-        <v>1752706164500</v>
+        <v>88315692060</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>333000</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>129000</v>
+        <v>213000</v>
       </c>
       <c r="S13" t="n">
-        <v>65000</v>
+        <v>66000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 증시 및 반도체주 급등에 따른 200만 돌파 기대. 공급 부족 장기화 전망 및 AI 두뇌 역할 강조.</t>
+          <t>미국 원전주 상승세 및 중동 전쟁 종전 논의에 따른 기대감. 대차해지 운동 참여 독려 및 하반기 상승 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '공급 부족']</t>
+          <t>['원전주', '대차해지', '하반기 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19270</v>
+        <v>13870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+4.22%</t>
+          <t>'+4.05%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="H14" t="n">
-        <v>10.74</v>
+        <v>4.92</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18490</v>
+        <v>13330</v>
       </c>
       <c r="K14" t="n">
-        <v>18900</v>
+        <v>13600</v>
       </c>
       <c r="L14" t="n">
-        <v>19700</v>
+        <v>13930</v>
       </c>
       <c r="M14" t="n">
-        <v>18770</v>
+        <v>13210</v>
       </c>
       <c r="N14" t="n">
-        <v>10.85</v>
+        <v>4.99</v>
       </c>
       <c r="O14" t="n">
-        <v>84506803715</v>
+        <v>38716469760</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>30200</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>3540</v>
       </c>
       <c r="R14" t="n">
-        <v>213000</v>
+        <v>-39000</v>
       </c>
       <c r="S14" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 원전주 상승세 및 중동 전쟁 종전 논의에 따른 기대감. 대차해지 운동 참여 독려 및 하반기 상승 전망.</t>
+          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전주', '대차해지', '하반기 전망']</t>
+          <t>['미국원전주', '매물대', '목표가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>259000</v>
+        <v>13810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.57%</t>
+          <t>'+3.37%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>482</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>1700</v>
+        <v>180</v>
       </c>
       <c r="H15" t="n">
-        <v>46.48</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>252500</v>
+        <v>13360</v>
       </c>
       <c r="K15" t="n">
-        <v>261000</v>
+        <v>13450</v>
       </c>
       <c r="L15" t="n">
-        <v>261000</v>
+        <v>14450</v>
       </c>
       <c r="M15" t="n">
-        <v>257500</v>
+        <v>13450</v>
       </c>
       <c r="N15" t="n">
-        <v>46.52</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1006476322750</v>
+        <v>28698129445</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q15" t="n">
-        <v>78600</v>
+        <v>3200</v>
       </c>
       <c r="R15" t="n">
-        <v>-509000</v>
+        <v>55000</v>
       </c>
       <c r="S15" t="n">
-        <v>226000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>엔비디아 칩 판매량 증가 뉴스에도 불구하고, 정치적 이슈 및 시장 전반의 약세에 대한 언급. 주가 상승에 대한 불확실성 존재.</t>
+          <t>호남반도체 관련 기대감 있으나, 실적 부진 및 급락 가능성에 대한 경고. 금호전기와의 비교 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['엔비디아', '반도체', '주가 상승']</t>
+          <t>['호남반도체', '실적', '급락']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17570</v>
+        <v>259000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.86%</t>
+          <t>'+2.57%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.27</v>
+        <v>-0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>478</v>
       </c>
       <c r="G16" t="n">
-        <v>117</v>
+        <v>1640</v>
       </c>
       <c r="H16" t="n">
-        <v>0.97</v>
+        <v>46.48</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17250</v>
+        <v>252500</v>
       </c>
       <c r="K16" t="n">
-        <v>17920</v>
+        <v>261000</v>
       </c>
       <c r="L16" t="n">
-        <v>18440</v>
+        <v>261000</v>
       </c>
       <c r="M16" t="n">
-        <v>17450</v>
+        <v>257500</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7</v>
+        <v>46.52</v>
       </c>
       <c r="O16" t="n">
-        <v>65778626425</v>
+        <v>1058509974500</v>
       </c>
       <c r="P16" t="n">
-        <v>30550</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>6100</v>
+        <v>78600</v>
       </c>
       <c r="R16" t="n">
-        <v>-82000</v>
+        <v>-509000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>226000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터주 급등에 따른 엑스게이트 기대감. 단기 과열 및 매도 의견 상존.</t>
+          <t>주가 상승에 대한 기대감보다는 정치적 이슈와 관련된 부정적 언급이 주를 이룸. 40만 전자 달성에 대한 장기적 관점 존재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보안주', '단기과열']</t>
+          <t>['정치', '개혁', '저평가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>85750</v>
+        <v>17680</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.41%</t>
+          <t>'+2.49%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.04</v>
+        <v>0.27</v>
       </c>
       <c r="E17" t="n">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>818</v>
+        <v>126</v>
       </c>
       <c r="H17" t="n">
-        <v>23.23</v>
+        <v>0.97</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>85400</v>
+        <v>17250</v>
       </c>
       <c r="K17" t="n">
-        <v>87300</v>
+        <v>17920</v>
       </c>
       <c r="L17" t="n">
-        <v>87800</v>
+        <v>18440</v>
       </c>
       <c r="M17" t="n">
-        <v>85300</v>
+        <v>17450</v>
       </c>
       <c r="N17" t="n">
-        <v>23.27</v>
+        <v>0.7</v>
       </c>
       <c r="O17" t="n">
-        <v>69232029800</v>
+        <v>66598364225</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>30550</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>6100</v>
       </c>
       <c r="R17" t="n">
-        <v>-105000</v>
+        <v>-82000</v>
       </c>
       <c r="S17" t="n">
-        <v>-48000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 증시 원전주 급등에 따른 국내 원전주 동반 상승 기대감. 대미 투자 관련 발표 가능성 및 120일선 돌파 가능성 언급.</t>
+          <t>미증시 양자컴퓨터 주식 급등에 따른 관련주 동반 상승 기대감. 단기 과열 우려 및 개인 투자자 포지션에 대한 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전주', '대미투자', '120일선']</t>
+          <t>['양자컴퓨터', '보안주', 'AI 반도체']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4245</v>
+        <v>85700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.41%</t>
+          <t>'+0.35%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.4</v>
+        <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="G18" t="n">
-        <v>629</v>
+        <v>823</v>
       </c>
       <c r="H18" t="n">
-        <v>0.55</v>
+        <v>23.23</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4635</v>
+        <v>85400</v>
       </c>
       <c r="K18" t="n">
-        <v>4465</v>
+        <v>87300</v>
       </c>
       <c r="L18" t="n">
-        <v>4535</v>
+        <v>87800</v>
       </c>
       <c r="M18" t="n">
-        <v>4165</v>
+        <v>85300</v>
       </c>
       <c r="N18" t="n">
-        <v>0.95</v>
+        <v>23.27</v>
       </c>
       <c r="O18" t="n">
-        <v>27973253872</v>
+        <v>71005582350</v>
       </c>
       <c r="P18" t="n">
-        <v>6900</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>1738</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>60000</v>
+        <v>-105000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미버스랩스 STO 사업 추진 및 미국 코인 주식거래 허용 호재. 그러나 급락 및 공매도 우려.</t>
+          <t>미국 증시 원전주 급등에 따른 국내 원전주 동반 상승 기대감. 대미 투자 관련 발표 가능성 및 120일선 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['STO', '암호화폐', '공매도']</t>
+          <t>['원전주', '대미투자', '120일선']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,97 +2120,281 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30</v>
+        <v>10180</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-30.23%</t>
+          <t>'-3.05%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G19" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="H19" t="n">
-        <v>3.69</v>
+        <v>1.24</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>43</v>
+        <v>10500</v>
       </c>
       <c r="K19" t="n">
-        <v>44</v>
+        <v>10650</v>
       </c>
       <c r="L19" t="n">
-        <v>44</v>
+        <v>10710</v>
       </c>
       <c r="M19" t="n">
-        <v>26</v>
+        <v>10100</v>
       </c>
       <c r="N19" t="n">
-        <v>3.71</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>90362757</v>
+        <v>19829207995</v>
       </c>
       <c r="P19" t="n">
-        <v>901</v>
+        <v>15960</v>
       </c>
       <c r="Q19" t="n">
-        <v>26</v>
+        <v>3500</v>
       </c>
       <c r="R19" t="n">
-        <v>-58000</v>
+        <v>-22000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>원풍물산, 장외거래 및 대주주 관련 언급. 기술 개발 기대감 있으나 급락 및 매도세 강함.</t>
+          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['장외거래', '기술 개발', '급락']</t>
+          <t>['미프진', '재료소멸', '하한가']</t>
         </is>
       </c>
       <c r="X19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>004310</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4190</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>'-9.60%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>159</v>
+      </c>
+      <c r="F20" t="n">
+        <v>100</v>
+      </c>
+      <c r="G20" t="n">
+        <v>639</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>4635</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4465</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4535</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4165</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O20" t="n">
+        <v>29034500789</v>
+      </c>
+      <c r="P20" t="n">
+        <v>6900</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1738</v>
+      </c>
+      <c r="R20" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>계열사 STO 사업 추진 및 미국 코인 관련 주식 거래 허용 호재 기대, 그러나 공매도 및 경고 예고로 인한 부정적 전망.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['STO', '코인', '공매도']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>201490</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>원풍물산</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>30</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>'-30.23%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E21" t="n">
+        <v>55</v>
+      </c>
+      <c r="F21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G21" t="n">
+        <v>99</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>43</v>
+      </c>
+      <c r="K21" t="n">
+        <v>44</v>
+      </c>
+      <c r="L21" t="n">
+        <v>44</v>
+      </c>
+      <c r="M21" t="n">
+        <v>26</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O21" t="n">
+        <v>90362757</v>
+      </c>
+      <c r="P21" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>26</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-58000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>K-OTC 시장에서의 원풍물산 주가 하락 지속. 대주주 지분 관련 및 기술 개발 협력 사실 언급에도 불구하고 투자 심리 위축.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['K-OTC', '대주주', '기술개발']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
         <v>2</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>008290</t>
         </is>
